--- a/evaluation_results.xlsx
+++ b/evaluation_results.xlsx
@@ -20,6 +20,12 @@
     <sheet name="ConstrainedOpenDoorLoc_2c_Missi" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="ConstrainedOpenDoorsOrder_1c_Mi" sheetId="12" state="visible" r:id="rId12"/>
     <sheet name="ConstrainedOpenDoorsOrder_2c_Mi" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="ConstrainedGoToOpen_1c_Missions" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="ConstrainedGoToOpen_2c_Missions" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="ConstrainedFindObjS5_1c_Mission" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet name="ConstrainedFindObjS5_2c_Mission" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="ConstrainedActionObjDoor_1c_Mis" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet name="ConstrainedActionObjDoor_2c_Mis" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1161,6 +1167,318 @@
       </c>
       <c r="P14" t="n">
         <v>73.89</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ConstrainedGoToOpen (1c)</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>2</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>67</v>
+      </c>
+      <c r="F15" t="n">
+        <v>455.7</v>
+      </c>
+      <c r="G15" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="H15" t="n">
+        <v>53</v>
+      </c>
+      <c r="I15" t="n">
+        <v>555.7</v>
+      </c>
+      <c r="J15" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="K15" t="n">
+        <v>52</v>
+      </c>
+      <c r="L15" t="n">
+        <v>569.2</v>
+      </c>
+      <c r="M15" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>42</v>
+      </c>
+      <c r="O15" t="n">
+        <v>678.5</v>
+      </c>
+      <c r="P15" t="n">
+        <v>24.71</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ConstrainedGoToOpen (2c)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>57</v>
+      </c>
+      <c r="F16" t="n">
+        <v>539.4</v>
+      </c>
+      <c r="G16" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>62</v>
+      </c>
+      <c r="I16" t="n">
+        <v>519.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="K16" t="n">
+        <v>66</v>
+      </c>
+      <c r="L16" t="n">
+        <v>489.4</v>
+      </c>
+      <c r="M16" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="N16" t="n">
+        <v>52</v>
+      </c>
+      <c r="O16" t="n">
+        <v>622.5</v>
+      </c>
+      <c r="P16" t="n">
+        <v>38.58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ConstrainedFindObjS5 (1c)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>5</v>
+      </c>
+      <c r="C17" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E17" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="F17" t="n">
+        <v>647.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="H17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>689.1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="K17" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>646.3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="N17" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>830.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>36.13</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ConstrainedFindObjS5 (2c)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>5</v>
+      </c>
+      <c r="C18" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E18" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="F18" t="n">
+        <v>696.1</v>
+      </c>
+      <c r="G18" t="n">
+        <v>77</v>
+      </c>
+      <c r="H18" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" t="n">
+        <v>727.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="K18" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>659.2</v>
+      </c>
+      <c r="M18" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="N18" t="n">
+        <v>20</v>
+      </c>
+      <c r="O18" t="n">
+        <v>867.4</v>
+      </c>
+      <c r="P18" t="n">
+        <v>75.93000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ConstrainedActionObjDoor (1c)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E19" t="n">
+        <v>55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>536.4</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H19" t="n">
+        <v>54</v>
+      </c>
+      <c r="I19" t="n">
+        <v>536.2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="K19" t="n">
+        <v>65</v>
+      </c>
+      <c r="L19" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="N19" t="n">
+        <v>42</v>
+      </c>
+      <c r="O19" t="n">
+        <v>687.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>22.58</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ConstrainedActionObjDoor (2c)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>8</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E20" t="n">
+        <v>75</v>
+      </c>
+      <c r="F20" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H20" t="n">
+        <v>48</v>
+      </c>
+      <c r="I20" t="n">
+        <v>630.1</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>48</v>
+      </c>
+      <c r="L20" t="n">
+        <v>621.9</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="N20" t="n">
+        <v>38</v>
+      </c>
+      <c r="O20" t="n">
+        <v>727.9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>55.95</v>
       </c>
     </row>
   </sheetData>
@@ -3394,6 +3712,2728 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>C-LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Random SR%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Random Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>go to the green box and avoid lava</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C2" t="n">
+        <v>732.7</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F2" t="n">
+        <v>900.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I2" t="n">
+        <v>712.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="n">
+        <v>796.3</v>
+      </c>
+      <c r="M2" t="n">
+        <v>27.8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>go to the red box and avoid lava</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3" t="n">
+        <v>615.3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>771.5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" t="n">
+        <v>745.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>30</v>
+      </c>
+      <c r="L3" t="n">
+        <v>856.2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>go to the blue box and avoid water</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" t="n">
+        <v>312.4</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>80</v>
+      </c>
+      <c r="F4" t="n">
+        <v>275</v>
+      </c>
+      <c r="G4" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>70</v>
+      </c>
+      <c r="I4" t="n">
+        <v>461</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>40</v>
+      </c>
+      <c r="L4" t="n">
+        <v>670</v>
+      </c>
+      <c r="M4" t="n">
+        <v>26.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>go to the grey box and avoid water</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C5" t="n">
+        <v>298.3</v>
+      </c>
+      <c r="D5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>80</v>
+      </c>
+      <c r="F5" t="n">
+        <v>272.2</v>
+      </c>
+      <c r="G5" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>70</v>
+      </c>
+      <c r="I5" t="n">
+        <v>327.1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>70</v>
+      </c>
+      <c r="L5" t="n">
+        <v>359.8</v>
+      </c>
+      <c r="M5" t="n">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>go to the yellow box and avoid water</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" t="n">
+        <v>430.8</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E6" t="n">
+        <v>80</v>
+      </c>
+      <c r="F6" t="n">
+        <v>322.4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>50</v>
+      </c>
+      <c r="I6" t="n">
+        <v>546</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>50</v>
+      </c>
+      <c r="L6" t="n">
+        <v>569.8</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>go to the red box and avoid water</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>80</v>
+      </c>
+      <c r="C7" t="n">
+        <v>337.1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>702.9</v>
+      </c>
+      <c r="G7" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>60</v>
+      </c>
+      <c r="I7" t="n">
+        <v>427.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" t="n">
+        <v>538.2</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>go to the purple box and avoid water</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
+        <v>269.3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>19.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>70</v>
+      </c>
+      <c r="F8" t="n">
+        <v>382.4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="H8" t="n">
+        <v>70</v>
+      </c>
+      <c r="I8" t="n">
+        <v>421.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>90</v>
+      </c>
+      <c r="L8" t="n">
+        <v>448.3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>go to the red box and avoid grass</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" t="n">
+        <v>515.5</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>633.5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H9" t="n">
+        <v>60</v>
+      </c>
+      <c r="I9" t="n">
+        <v>543.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>842.5</v>
+      </c>
+      <c r="M9" t="n">
+        <v>21.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>go to the grey box and avoid lava</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="n">
+        <v>596.4</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>40</v>
+      </c>
+      <c r="F10" t="n">
+        <v>678</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="H10" t="n">
+        <v>20</v>
+      </c>
+      <c r="I10" t="n">
+        <v>803.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>20</v>
+      </c>
+      <c r="L10" t="n">
+        <v>882.9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>19.2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>go to the purple box and avoid grass</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>60</v>
+      </c>
+      <c r="C11" t="n">
+        <v>448.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>618.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>47.7</v>
+      </c>
+      <c r="H11" t="n">
+        <v>40</v>
+      </c>
+      <c r="I11" t="n">
+        <v>703</v>
+      </c>
+      <c r="J11" t="n">
+        <v>53.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="n">
+        <v>821.3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>40.7</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>455.7</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>555.7</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>13.81</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>569.2</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>678.5</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>24.71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>C-LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Random SR%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Random Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>go to the green box and avoid lava and avoid grass</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>40</v>
+      </c>
+      <c r="C2" t="n">
+        <v>682</v>
+      </c>
+      <c r="D2" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2" t="n">
+        <v>757.9</v>
+      </c>
+      <c r="G2" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="H2" t="n">
+        <v>60</v>
+      </c>
+      <c r="I2" t="n">
+        <v>591.2</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.6</v>
+      </c>
+      <c r="K2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L2" t="n">
+        <v>809.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>go to the red box and avoid lava and avoid grass</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>10</v>
+      </c>
+      <c r="C3" t="n">
+        <v>951.8</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="n">
+        <v>817</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>30</v>
+      </c>
+      <c r="I3" t="n">
+        <v>754.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>26.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>40</v>
+      </c>
+      <c r="L3" t="n">
+        <v>680.3</v>
+      </c>
+      <c r="M3" t="n">
+        <v>86.90000000000001</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>go to the blue box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>60</v>
+      </c>
+      <c r="C4" t="n">
+        <v>503.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="E4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F4" t="n">
+        <v>539.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>40.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>70</v>
+      </c>
+      <c r="I4" t="n">
+        <v>478</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="K4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" t="n">
+        <v>589.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>55.1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>go to the grey box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>90</v>
+      </c>
+      <c r="C5" t="n">
+        <v>255.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" t="n">
+        <v>435.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>80</v>
+      </c>
+      <c r="I5" t="n">
+        <v>346.4</v>
+      </c>
+      <c r="J5" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="K5" t="n">
+        <v>60</v>
+      </c>
+      <c r="L5" t="n">
+        <v>531</v>
+      </c>
+      <c r="M5" t="n">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>go to the yellow box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
+      </c>
+      <c r="C6" t="n">
+        <v>410.5</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E6" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" t="n">
+        <v>437.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="H6" t="n">
+        <v>90</v>
+      </c>
+      <c r="I6" t="n">
+        <v>329.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>60</v>
+      </c>
+      <c r="L6" t="n">
+        <v>531.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>43.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>go to the red box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="n">
+        <v>444.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>547.1</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>70</v>
+      </c>
+      <c r="I7" t="n">
+        <v>412.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="K7" t="n">
+        <v>60</v>
+      </c>
+      <c r="L7" t="n">
+        <v>571</v>
+      </c>
+      <c r="M7" t="n">
+        <v>29.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>go to the purple box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>90</v>
+      </c>
+      <c r="C8" t="n">
+        <v>258.7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>9</v>
+      </c>
+      <c r="E8" t="n">
+        <v>80</v>
+      </c>
+      <c r="F8" t="n">
+        <v>288.7</v>
+      </c>
+      <c r="G8" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H8" t="n">
+        <v>90</v>
+      </c>
+      <c r="I8" t="n">
+        <v>253.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>7.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>80</v>
+      </c>
+      <c r="L8" t="n">
+        <v>338.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>go to the red box and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" t="n">
+        <v>652.7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="n">
+        <v>80</v>
+      </c>
+      <c r="F9" t="n">
+        <v>425</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>40</v>
+      </c>
+      <c r="I9" t="n">
+        <v>654.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="K9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L9" t="n">
+        <v>830.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>go to the grey box and avoid lava and avoid grass</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>50</v>
+      </c>
+      <c r="C10" t="n">
+        <v>647.5</v>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>60</v>
+      </c>
+      <c r="F10" t="n">
+        <v>461.6</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H10" t="n">
+        <v>70</v>
+      </c>
+      <c r="I10" t="n">
+        <v>552.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>50</v>
+      </c>
+      <c r="L10" t="n">
+        <v>665</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>go to the purple box and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>50</v>
+      </c>
+      <c r="C11" t="n">
+        <v>586.4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>43.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" t="n">
+        <v>483.6</v>
+      </c>
+      <c r="G11" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="H11" t="n">
+        <v>60</v>
+      </c>
+      <c r="I11" t="n">
+        <v>521.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>72.09999999999999</v>
+      </c>
+      <c r="K11" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" t="n">
+        <v>677.8</v>
+      </c>
+      <c r="M11" t="n">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>539.4</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>12.13</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>519.3</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>26.79</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>489.4</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>17.86</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>622.5</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>38.58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>C-LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Random SR%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Random Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pick up the box and avoid water</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>30</v>
+      </c>
+      <c r="C2" t="n">
+        <v>716</v>
+      </c>
+      <c r="D2" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="E2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F2" t="n">
+        <v>771.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I2" t="n">
+        <v>765.9</v>
+      </c>
+      <c r="J2" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>40</v>
+      </c>
+      <c r="L2" t="n">
+        <v>734.8</v>
+      </c>
+      <c r="M2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pick up the box and avoid lava</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>30</v>
+      </c>
+      <c r="C3" t="n">
+        <v>704</v>
+      </c>
+      <c r="D3" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F3" t="n">
+        <v>529.1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" t="n">
+        <v>645</v>
+      </c>
+      <c r="J3" t="n">
+        <v>34.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L3" t="n">
+        <v>919</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19.4</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pick up the box and avoid grass</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
+        <v>522.3</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>30</v>
+      </c>
+      <c r="F4" t="n">
+        <v>766.9</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>528.1</v>
+      </c>
+      <c r="J4" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L4" t="n">
+        <v>836.6</v>
+      </c>
+      <c r="M4" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>647.4</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>42.23</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>689.1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>38.17</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>46.7</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>646.3</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>830.1</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>36.13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>C-LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Random SR%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Random Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>pick up the box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2" t="n">
+        <v>840.3</v>
+      </c>
+      <c r="D2" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F2" t="n">
+        <v>806.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>47.2</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20</v>
+      </c>
+      <c r="I2" t="n">
+        <v>858.8</v>
+      </c>
+      <c r="J2" t="n">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="K2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L2" t="n">
+        <v>888.2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>86.5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pick up the box and avoid lava and avoid grass</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>40</v>
+      </c>
+      <c r="C3" t="n">
+        <v>614.4</v>
+      </c>
+      <c r="D3" t="n">
+        <v>73</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>729.2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" t="n">
+        <v>491.3</v>
+      </c>
+      <c r="J3" t="n">
+        <v>59</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>883.7</v>
+      </c>
+      <c r="M3" t="n">
+        <v>66.7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pick up the box and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C4" t="n">
+        <v>633.6</v>
+      </c>
+      <c r="D4" t="n">
+        <v>44.7</v>
+      </c>
+      <c r="E4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F4" t="n">
+        <v>646</v>
+      </c>
+      <c r="G4" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>50</v>
+      </c>
+      <c r="I4" t="n">
+        <v>627.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>20</v>
+      </c>
+      <c r="L4" t="n">
+        <v>830.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>74.59999999999999</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>696.1</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>727.2</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>68.27</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>659.2</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>867.4</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>75.93000000000001</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>C-LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Random SR%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Random Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>go to the grey door and avoid grass</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>80</v>
+      </c>
+      <c r="C2" t="n">
+        <v>319.1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>90</v>
+      </c>
+      <c r="F2" t="n">
+        <v>175.4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>80</v>
+      </c>
+      <c r="I2" t="n">
+        <v>395.6</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>30</v>
+      </c>
+      <c r="L2" t="n">
+        <v>764.6</v>
+      </c>
+      <c r="M2" t="n">
+        <v>25.3</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pick up the blue box and avoid grass</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>60</v>
+      </c>
+      <c r="C3" t="n">
+        <v>451.7</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F3" t="n">
+        <v>791.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>60</v>
+      </c>
+      <c r="I3" t="n">
+        <v>568.6</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="K3" t="n">
+        <v>70</v>
+      </c>
+      <c r="L3" t="n">
+        <v>488.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pick up the red box and avoid grass</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C4" t="n">
+        <v>623.2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E4" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" t="n">
+        <v>408.1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>90</v>
+      </c>
+      <c r="I4" t="n">
+        <v>330.4</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>30</v>
+      </c>
+      <c r="L4" t="n">
+        <v>797.3</v>
+      </c>
+      <c r="M4" t="n">
+        <v>25.2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pick up the grey box and avoid water</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>40</v>
+      </c>
+      <c r="C5" t="n">
+        <v>770</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F5" t="n">
+        <v>694.3</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>60</v>
+      </c>
+      <c r="I5" t="n">
+        <v>482.7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>50</v>
+      </c>
+      <c r="L5" t="n">
+        <v>663.2</v>
+      </c>
+      <c r="M5" t="n">
+        <v>29.8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pick up the grey box and avoid lava</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>60</v>
+      </c>
+      <c r="C6" t="n">
+        <v>484.7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F6" t="n">
+        <v>782.5</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>60</v>
+      </c>
+      <c r="I6" t="n">
+        <v>442.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>40</v>
+      </c>
+      <c r="L6" t="n">
+        <v>704.4</v>
+      </c>
+      <c r="M6" t="n">
+        <v>18.9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pick up the yellow box and avoid water</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="n">
+        <v>442.9</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>50</v>
+      </c>
+      <c r="F7" t="n">
+        <v>633.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="n">
+        <v>616.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>50</v>
+      </c>
+      <c r="L7" t="n">
+        <v>556.5</v>
+      </c>
+      <c r="M7" t="n">
+        <v>20.2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pick up the blue box and avoid water</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" t="n">
+        <v>675</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" t="n">
+        <v>527.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>50</v>
+      </c>
+      <c r="I8" t="n">
+        <v>567.5</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>40</v>
+      </c>
+      <c r="L8" t="n">
+        <v>777.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pick up the blue box and avoid lava</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C9" t="n">
+        <v>719.4</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="E9" t="n">
+        <v>20</v>
+      </c>
+      <c r="F9" t="n">
+        <v>802.2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>580.6</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="M9" t="n">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>go to the grey box and avoid grass</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n">
+        <v>65.09999999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>125.7</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" t="n">
+        <v>115</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" t="n">
+        <v>383.1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pick up the green box and avoid water</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>812.5</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="n">
+        <v>60</v>
+      </c>
+      <c r="F11" t="n">
+        <v>421.7</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>60</v>
+      </c>
+      <c r="I11" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="n">
+        <v>30</v>
+      </c>
+      <c r="L11" t="n">
+        <v>738.2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>536.4</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>536.2</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>455.6</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>687.4</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>22.58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Mission</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>C-LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>C-LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML SR%</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Steps</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>NN_C_LAMAML Viols</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Random SR%</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Steps</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Random Viols</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>go to the grey door and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C2" t="n">
+        <v>439.2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>80</v>
+      </c>
+      <c r="F2" t="n">
+        <v>413</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>70</v>
+      </c>
+      <c r="I2" t="n">
+        <v>538.7</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K2" t="n">
+        <v>60</v>
+      </c>
+      <c r="L2" t="n">
+        <v>530.1</v>
+      </c>
+      <c r="M2" t="n">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>pick up the blue box and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>70</v>
+      </c>
+      <c r="C3" t="n">
+        <v>430.9</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>20</v>
+      </c>
+      <c r="F3" t="n">
+        <v>810</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" t="n">
+        <v>695.8</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K3" t="n">
+        <v>20</v>
+      </c>
+      <c r="L3" t="n">
+        <v>825.9</v>
+      </c>
+      <c r="M3" t="n">
+        <v>67.09999999999999</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>pick up the red box and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>90</v>
+      </c>
+      <c r="C4" t="n">
+        <v>232.1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" t="n">
+        <v>853</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20</v>
+      </c>
+      <c r="I4" t="n">
+        <v>873.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K4" t="n">
+        <v>60</v>
+      </c>
+      <c r="L4" t="n">
+        <v>626.2</v>
+      </c>
+      <c r="M4" t="n">
+        <v>47.4</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>pick up the grey box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>70</v>
+      </c>
+      <c r="C5" t="n">
+        <v>405.7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50</v>
+      </c>
+      <c r="F5" t="n">
+        <v>657.7</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" t="n">
+        <v>779.8</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" t="n">
+        <v>758.7</v>
+      </c>
+      <c r="M5" t="n">
+        <v>58.2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>pick up the grey box and avoid lava and avoid grass</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>70</v>
+      </c>
+      <c r="C6" t="n">
+        <v>585.1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50</v>
+      </c>
+      <c r="F6" t="n">
+        <v>670.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>20</v>
+      </c>
+      <c r="I6" t="n">
+        <v>830.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>30</v>
+      </c>
+      <c r="L6" t="n">
+        <v>861.5</v>
+      </c>
+      <c r="M6" t="n">
+        <v>91.90000000000001</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>pick up the yellow box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="n">
+        <v>529</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E7" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" t="n">
+        <v>621</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" t="n">
+        <v>662.9</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>30</v>
+      </c>
+      <c r="L7" t="n">
+        <v>826.9</v>
+      </c>
+      <c r="M7" t="n">
+        <v>52.5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>pick up the blue box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>80</v>
+      </c>
+      <c r="C8" t="n">
+        <v>342.8</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" t="n">
+        <v>638.3</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>60</v>
+      </c>
+      <c r="I8" t="n">
+        <v>459.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
+        <v>10</v>
+      </c>
+      <c r="L8" t="n">
+        <v>921.6</v>
+      </c>
+      <c r="M8" t="n">
+        <v>35.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>pick up the blue box and avoid lava and avoid grass</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>90</v>
+      </c>
+      <c r="C9" t="n">
+        <v>320</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50</v>
+      </c>
+      <c r="F9" t="n">
+        <v>724.7</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" t="n">
+        <v>553.4</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>40</v>
+      </c>
+      <c r="L9" t="n">
+        <v>698.8</v>
+      </c>
+      <c r="M9" t="n">
+        <v>64.8</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>go to the grey box and avoid lava and avoid water</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>90</v>
+      </c>
+      <c r="C10" t="n">
+        <v>200.7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F10" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>100</v>
+      </c>
+      <c r="I10" t="n">
+        <v>79.09999999999999</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>80</v>
+      </c>
+      <c r="L10" t="n">
+        <v>398.9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>28.9</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>pick up the green box and avoid grass and avoid water</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>70</v>
+      </c>
+      <c r="C11" t="n">
+        <v>473.8</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E11" t="n">
+        <v>30</v>
+      </c>
+      <c r="F11" t="n">
+        <v>806.3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>40</v>
+      </c>
+      <c r="I11" t="n">
+        <v>746</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>20</v>
+      </c>
+      <c r="L11" t="n">
+        <v>830.6</v>
+      </c>
+      <c r="M11" t="n">
+        <v>57.9</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>OVERALL</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>395.9</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>630.1</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>621.9</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>727.9</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>55.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
